--- a/AAII_Financials/Quarterly/PSZKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSZKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>PSZKY</t>
   </si>
@@ -656,75 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,8 +773,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,8 +823,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +873,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -883,8 +895,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -930,8 +943,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -977,8 +993,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1024,8 +1043,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1071,8 +1093,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1087,8 +1112,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1134,8 +1160,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,8 +1210,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1200,8 +1232,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1247,8 +1280,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1294,8 +1330,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1341,8 +1380,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1388,8 +1430,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1435,8 +1480,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1482,8 +1530,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1529,8 +1580,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1576,8 +1630,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1623,8 +1680,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,8 +1730,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1717,8 +1780,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1764,8 +1830,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1811,8 +1880,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1858,8 +1930,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1905,8 +1980,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1952,60 +2030,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2023,8 +2107,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2042,431 +2127,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4189000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4539200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6670200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5256000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5875100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3888600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6602700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5131200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4356300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4003200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7683300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3770400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3416900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3383100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7195500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2290800</v>
+        <v>1163800</v>
       </c>
       <c r="E42" s="3">
+        <v>2037700</v>
+      </c>
+      <c r="F42" s="3">
         <v>1333200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>766300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2650900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2284300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>810800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3949100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4294600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4340300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1393600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5242000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7099300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6455100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3289600</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>654600</v>
+        <v>2292500</v>
       </c>
       <c r="E43" s="3">
+        <v>655400</v>
+      </c>
+      <c r="F43" s="3">
         <v>952800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3161600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>472600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>294300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>414200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>379000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>453200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>316300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>384300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>362400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>419000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>467200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>59000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>51800</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>52400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>89800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4000</v>
+        <v>3301600</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>620300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1956300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>625500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>193100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>88800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>108900</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7488700</v>
+        <v>10946900</v>
       </c>
       <c r="E46" s="3">
+        <v>7232600</v>
+      </c>
+      <c r="F46" s="3">
         <v>9680300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9184700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10954900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6478500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8546300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9469200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9108800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8662100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9749500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9377800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11163500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10307400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10935900</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>64421000</v>
+        <v>63221400</v>
       </c>
       <c r="E47" s="3">
+        <v>66036600</v>
+      </c>
+      <c r="F47" s="3">
         <v>65880700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>61313500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>58683300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54455200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48857700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49952900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47908000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46845600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47567100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37863900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37657300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31616600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>28856500</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1754900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1772300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1817400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>761900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1671400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1551200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1445200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1490500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1378400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1375100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1353200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1171200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1190800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1095500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1069100</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1106700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1111200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1164300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>911500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1135700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1054800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1004800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1009200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>965500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>972400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>996600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>850900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>906900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>806700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>802100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2512,8 +2625,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2559,55 +2675,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2374000</v>
+        <v>402600</v>
       </c>
       <c r="E52" s="3">
+        <v>1015400</v>
+      </c>
+      <c r="F52" s="3">
         <v>1334900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>840800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1140100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2718700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2089000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3148200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2667500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2605500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2806800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2885400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2786800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2951200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2491200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2653,55 +2775,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161705200</v>
+      </c>
+      <c r="E54" s="3">
         <v>159388000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>162254800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>145736100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>151521600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137162800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>127080800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>133150200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>126164800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124845500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>126005100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108270900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113382200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>103091000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>98535400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2719,8 +2847,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2738,290 +2867,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>126636600</v>
+        <v>127077600</v>
       </c>
       <c r="E57" s="3">
+        <v>127043000</v>
+      </c>
+      <c r="F57" s="3">
         <v>129146300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120648600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120097500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>109061200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>102162600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>105917100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>99988100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>99295400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>102272700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>86953400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>90745000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>81149800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>78086600</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>672100</v>
+      </c>
+      <c r="E58" s="3">
         <v>731700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4058600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>519100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>624600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>694600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2691000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2054900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2426800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2765800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4005600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2626700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3805400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3849600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6418900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2166000</v>
+      </c>
+      <c r="E59" s="3">
         <v>850600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1294500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>141600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>285200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>176600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>545100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>372000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>330800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>448200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1369500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>272400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>431000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>301900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>501100</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>128223400</v>
+        <v>129920000</v>
       </c>
       <c r="E60" s="3">
+        <v>128629800</v>
+      </c>
+      <c r="F60" s="3">
         <v>134785200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>121309400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>121010500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>109935500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>105608800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>108388200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>102790100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>102547200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>107983200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>89884400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95131000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85331000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85169200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11395300</v>
+      </c>
+      <c r="E61" s="3">
         <v>9762000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7335500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5546900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8639000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7530900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5257900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7144400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6418200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6064100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3368200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5025900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5527100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6037800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3158800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5073900</v>
+        <v>5302800</v>
       </c>
       <c r="E62" s="3">
+        <v>4667500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3149200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4405200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7237300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5169700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3020600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4262800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5077600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4066000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2691600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2799600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2289600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2577400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1894200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3067,8 +3215,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3114,8 +3265,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3161,55 +3315,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>146848000</v>
+      </c>
+      <c r="E66" s="3">
         <v>143319400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>145975100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>131261500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>137144200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>122869200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114409600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>120019000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114491900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112880600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>114501300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97876000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103264100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>93978900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90380500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3227,8 +3387,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3274,8 +3435,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3321,8 +3485,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3368,8 +3535,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3415,55 +3585,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4672700</v>
+      </c>
+      <c r="E72" s="3">
         <v>6842900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6392800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5035700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4852400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6238400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5249900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5010700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4175000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4879900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4421200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3816700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3417600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3426300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3038000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3509,8 +3685,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3556,8 +3735,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3603,55 +3785,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14860100</v>
+      </c>
+      <c r="E76" s="3">
         <v>16071800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16282800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14474500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14380400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14296400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12673800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13133900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11675900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11967900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11506500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10398100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10121300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9115600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8158100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3697,60 +3885,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3796,8 +3990,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3815,55 +4012,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E83" s="3">
         <v>51400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>128200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-37000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3909,8 +4110,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3956,8 +4160,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4003,8 +4210,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4050,8 +4260,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4097,55 +4310,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4456900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2059200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3418900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2230300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1052000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1292500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1825300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2826700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-677300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1584400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>348000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>703300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-944300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2077200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>560200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4163,55 +4382,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-233700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-178100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-159200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-107400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-126700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4257,8 +4480,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4304,55 +4530,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>697400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-237300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3582200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>102600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>933300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1331500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1654200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1261700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1467300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4591900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2110500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3209500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1686000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-764900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4370,41 +4602,42 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>1883500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>842600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>401900</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
@@ -4414,11 +4647,14 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4464,8 +4700,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4511,8 +4750,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4558,55 +4800,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2970200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2385500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6457000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1344300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2319800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>954100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3305100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1821100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1912400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1424100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5584900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2284000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3805900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2826100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-570500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4652,51 +4900,57 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-789300</v>
+      </c>
+      <c r="E102" s="3">
         <v>89100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-544000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-783400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2201000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1669900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-174400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>256100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>734700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1541100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1341000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>876800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-347900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-937100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-775100</v>
       </c>
     </row>
